--- a/Programming Lab/كشف المحكمين.xlsx
+++ b/Programming Lab/كشف المحكمين.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30D2E361-9028-46A2-9AB9-6AA314C34CC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12570"/>
+    <workbookView xWindow="-19005" yWindow="-1380" windowWidth="17895" windowHeight="15285" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="قائمة التقييم" sheetId="2" r:id="rId1"/>
@@ -22,6 +23,9 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -533,22 +537,22 @@
     <t>سعيد سالم سعيد الحنطوبي</t>
   </si>
   <si>
-    <t>مجموعة لواء</t>
-  </si>
-  <si>
-    <t>كتيبة مشاة آلية</t>
-  </si>
-  <si>
-    <t>كتيبة دبابات</t>
-  </si>
-  <si>
-    <t>كتيبة المدفعية</t>
+    <t>قيادة مجموعة اللواء</t>
+  </si>
+  <si>
+    <t>قيادة كتيبة المشاة الآلية/2</t>
+  </si>
+  <si>
+    <t>قيادة كتيبة الدبابات/4</t>
+  </si>
+  <si>
+    <t>قيادة كتيبة المدفعية</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-10C0000]d\ mmmm\ yyyy;@"/>
   </numFmts>
@@ -1063,7 +1067,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -1197,7 +1201,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:I338"/>
   <sheetFormatPr defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2905,7 +2909,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>

--- a/Programming Lab/كشف المحكمين.xlsx
+++ b/Programming Lab/كشف المحكمين.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30D2E361-9028-46A2-9AB9-6AA314C34CC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A98E25C8-933A-4DF4-B3FB-4BFEA2C6639D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19005" yWindow="-1380" windowWidth="17895" windowHeight="15285" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5775" yWindow="1560" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="قائمة التقييم" sheetId="2" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="171">
   <si>
     <t>سرية الاستطلاع</t>
   </si>
@@ -519,18 +519,6 @@
     <t>أحمد عبدالله مبارك البلوشي</t>
   </si>
   <si>
-    <t>مدني/1</t>
-  </si>
-  <si>
-    <t>مدني/2</t>
-  </si>
-  <si>
-    <t>عارف عيضة الجابري</t>
-  </si>
-  <si>
-    <t>مدني/3</t>
-  </si>
-  <si>
     <t>عبدالله أحمد مبارك آل علي</t>
   </si>
   <si>
@@ -543,10 +531,19 @@
     <t>قيادة كتيبة المشاة الآلية/2</t>
   </si>
   <si>
-    <t>قيادة كتيبة الدبابات/4</t>
-  </si>
-  <si>
-    <t>قيادة كتيبة المدفعية</t>
+    <t>وكيل/1</t>
+  </si>
+  <si>
+    <t>مدني/4</t>
+  </si>
+  <si>
+    <t>سامح محمد حسان</t>
+  </si>
+  <si>
+    <t>قيادة كتيبة المدفعية/14</t>
+  </si>
+  <si>
+    <t>سعيد حمدان المرشدي</t>
   </si>
 </sst>
 </file>
@@ -1097,64 +1094,70 @@
     </row>
     <row r="2" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="21">
-        <v>123456</v>
+        <v>206109</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>161</v>
       </c>
       <c r="D2" s="18" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="21">
-        <v>654321</v>
+        <v>210560</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="D3" s="18" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="21">
-        <v>456789</v>
+        <v>123456</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D4" s="18" t="s">
-        <v>170</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="21">
-        <v>987654</v>
+        <v>654321</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C5" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="21">
+        <v>934042</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="D5" s="18" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="21"/>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
+      <c r="C6" s="4" t="s">
+        <v>168</v>
+      </c>
       <c r="D6" s="18"/>
     </row>
     <row r="7" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">

--- a/Programming Lab/كشف المحكمين.xlsx
+++ b/Programming Lab/كشف المحكمين.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A98E25C8-933A-4DF4-B3FB-4BFEA2C6639D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19F83B59-2098-410B-97F1-27C172CD1CE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5775" yWindow="1560" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="قائمة التقييم" sheetId="2" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="170">
   <si>
     <t>سرية الاستطلاع</t>
   </si>
@@ -526,9 +526,6 @@
   </si>
   <si>
     <t>قيادة مجموعة اللواء</t>
-  </si>
-  <si>
-    <t>قيادة كتيبة المشاة الآلية/2</t>
   </si>
   <si>
     <t>وكيل/1</t>
@@ -1097,7 +1094,7 @@
         <v>206109</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>161</v>
@@ -1111,13 +1108,13 @@
         <v>210560</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D3" s="18" t="s">
-        <v>165</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1125,7 +1122,7 @@
         <v>123456</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>162</v>
@@ -1139,13 +1136,13 @@
         <v>654321</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>163</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1153,10 +1150,10 @@
         <v>934042</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>167</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>168</v>
       </c>
       <c r="D6" s="18"/>
     </row>
